--- a/source.xlsx
+++ b/source.xlsx
@@ -1,55 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\live_meeting\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC2373D-B596-417A-B505-7CE2F15B6A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>회의명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의 유형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의일시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>참석자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의 목적</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결론 및 결정 사항</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>향후 계획</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요 안건 및 내용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR Black"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR DemiLight"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +122,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,76 +483,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:C12"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>회의명</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>회의 유형</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>회의일시</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>참석자</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>작성자</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>회의 목적</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>주요 내용</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>결론 및 향후 계획</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
+    <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B12" s="7"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>